--- a/rental_application_form_templates/041_real_estate_agent_contact_form--rental_application_form_templates.xlsx
+++ b/rental_application_form_templates/041_real_estate_agent_contact_form--rental_application_form_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1102,8 +1102,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'residential',_'value':_'residential'}</t>
+          <t>residential</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'residential', 'value': 'Residential'}</t>
+          <t>Residential</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'commercial',_'value':_'commercial'}</t>
+          <t>commercial</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'commercial', 'value': 'Commercial'}</t>
+          <t>Commercial</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'industrial',_'value':_'industrial'}</t>
+          <t>industrial</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'industrial', 'value': 'Industrial'}</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'available',_'value':_'available'}</t>
+          <t>available</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'available', 'value': 'Available'}</t>
+          <t>Available</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'rented',_'value':_'rented'}</t>
+          <t>rented</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'rented', 'value': 'Rented'}</t>
+          <t>Rented</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'sold',_'value':_'sold'}</t>
+          <t>sold</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'sold', 'value': 'Sold'}</t>
+          <t>Sold</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'phone',_'value':_'phone'}</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'phone', 'value': 'Phone'}</t>
+          <t>Phone</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'email',_'value':_'email'}</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'email', 'value': 'Email'}</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'message',_'value':_'message'}</t>
+          <t>message</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'message', 'value': 'Message'}</t>
+          <t>Message</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'agent',_'value':_'agent'}</t>
+          <t>agent</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'agent', 'value': 'Agent'}</t>
+          <t>Agent</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'online',_'value':_'online'}</t>
+          <t>online</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'online', 'value': 'Online'}</t>
+          <t>Online</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'referral',_'value':_'referral'}</t>
+          <t>referral</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'referral', 'value': 'Referral'}</t>
+          <t>Referral</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'print',_'value':_'print'}</t>
+          <t>print</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'print', 'value': 'Print'}</t>
+          <t>Print</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1352,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_5,_'name':_'social',_'value':_'social'}</t>
+          <t>social</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 5, 'name': 'social', 'value': 'Social'}</t>
+          <t>Social</t>
         </is>
       </c>
     </row>
@@ -1369,12 +1369,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'realty_company_1',_'value':_'realty_company_1'}</t>
+          <t>realty_company_1</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'realty_company_1', 'value': 'Realty Company 1'}</t>
+          <t>Realty Company 1</t>
         </is>
       </c>
     </row>
@@ -1386,12 +1386,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'realty_company_2',_'value':_'realty_company_2'}</t>
+          <t>realty_company_2</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'realty_company_2', 'value': 'Realty Company 2'}</t>
+          <t>Realty Company 2</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1403,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'realty_company_3',_'value':_'realty_company_3'}</t>
+          <t>realty_company_3</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'realty_company_3', 'value': 'Realty Company 3'}</t>
+          <t>Realty Company 3</t>
         </is>
       </c>
     </row>
@@ -1420,12 +1420,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'new',_'value':_'new'}</t>
+          <t>new</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'new', 'value': 'New'}</t>
+          <t>New</t>
         </is>
       </c>
     </row>
@@ -1437,12 +1437,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'follow_up',_'value':_'follow-up'}</t>
+          <t>follow-up</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'follow_up', 'value': 'Follow-up'}</t>
+          <t>Follow-up</t>
         </is>
       </c>
     </row>
@@ -1454,12 +1454,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'converted',_'value':_'converted'}</t>
+          <t>converted</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'converted', 'value': 'Converted'}</t>
+          <t>Converted</t>
         </is>
       </c>
     </row>
@@ -1471,12 +1471,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'expired',_'value':_'expired'}</t>
+          <t>expired</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'expired', 'value': 'Expired'}</t>
+          <t>Expired</t>
         </is>
       </c>
     </row>
